--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488263_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488263_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.7955</v>
+        <v>3.1637</v>
       </c>
       <c r="E2" t="n">
-        <v>3.173</v>
+        <v>3.3689</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.3775</v>
+        <v>-0.2051</v>
       </c>
       <c r="G2" t="n">
         <v>-0.439</v>
@@ -610,13 +610,13 @@
         <v>1.4823</v>
       </c>
       <c r="S2" t="n">
-        <v>0.1783</v>
+        <v>0.5465</v>
       </c>
       <c r="T2" t="n">
-        <v>0.5061</v>
+        <v>0.702</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.3278</v>
+        <v>-0.1555</v>
       </c>
       <c r="V2" t="n">
         <v>1.5738</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>F. NDIAYE</t>
+          <t>M. MALICK</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.6283</v>
+        <v>0.1921</v>
       </c>
       <c r="E4" t="n">
-        <v>1.1682</v>
+        <v>0.5515</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.5397999999999999</v>
+        <v>-0.3593</v>
       </c>
       <c r="G4" t="n">
-        <v>-7.0354</v>
+        <v>-2.7809</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.9221</v>
+        <v>0.228</v>
       </c>
       <c r="I4" t="n">
-        <v>-5.1133</v>
+        <v>-3.0089</v>
       </c>
       <c r="J4" t="n">
-        <v>-4.09</v>
+        <v>0.1097</v>
       </c>
       <c r="K4" t="n">
-        <v>-2.2558</v>
+        <v>0.669</v>
       </c>
       <c r="L4" t="n">
-        <v>-1.8342</v>
+        <v>-0.5592</v>
       </c>
       <c r="M4" t="n">
-        <v>-2.9454</v>
+        <v>-2.8907</v>
       </c>
       <c r="N4" t="n">
-        <v>0.3337</v>
+        <v>-0.441</v>
       </c>
       <c r="O4" t="n">
-        <v>-3.2791</v>
+        <v>-2.4497</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.9264</v>
+        <v>0.5558999999999999</v>
       </c>
       <c r="Q4" t="n">
-        <v>-3.7057</v>
+        <v>-1.8529</v>
       </c>
       <c r="R4" t="n">
-        <v>2.7793</v>
+        <v>2.4087</v>
       </c>
       <c r="S4" t="n">
-        <v>7.6463</v>
+        <v>-0.101</v>
       </c>
       <c r="T4" t="n">
-        <v>6.7612</v>
+        <v>0.4064</v>
       </c>
       <c r="U4" t="n">
-        <v>0.8851</v>
+        <v>-0.5074</v>
       </c>
       <c r="V4" t="n">
-        <v>0.9439</v>
+        <v>2.5183</v>
       </c>
       <c r="W4" t="n">
-        <v>2.2027</v>
+        <v>1.8883</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.2589</v>
+        <v>0.63</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. MALICK</t>
+          <t>A. FROUFE PEREZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.9218</v>
+        <v>-0.5493</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.4393</v>
+        <v>2.0258</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.4825</v>
+        <v>-2.5751</v>
       </c>
       <c r="G5" t="n">
-        <v>-2.7809</v>
+        <v>1.9964</v>
       </c>
       <c r="H5" t="n">
-        <v>0.228</v>
+        <v>3.6664</v>
       </c>
       <c r="I5" t="n">
-        <v>-3.0089</v>
+        <v>-1.6699</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1097</v>
+        <v>5.4324</v>
       </c>
       <c r="K5" t="n">
-        <v>0.669</v>
+        <v>4.2379</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.5592</v>
+        <v>1.1945</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.8907</v>
+        <v>-3.4359</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.441</v>
+        <v>-0.5715</v>
       </c>
       <c r="O5" t="n">
-        <v>-2.4497</v>
+        <v>-2.8644</v>
       </c>
       <c r="P5" t="n">
-        <v>0.5558999999999999</v>
+        <v>-1.4823</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.8529</v>
+        <v>-3.7057</v>
       </c>
       <c r="R5" t="n">
-        <v>2.4087</v>
+        <v>2.2234</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.2149</v>
+        <v>-0.1191</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.5844</v>
+        <v>0.6146</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.6304999999999999</v>
+        <v>-0.7337</v>
       </c>
       <c r="V5" t="n">
-        <v>2.5183</v>
+        <v>-0.9444</v>
       </c>
       <c r="W5" t="n">
-        <v>1.8883</v>
+        <v>-0.3155</v>
       </c>
       <c r="X5" t="n">
-        <v>0.63</v>
+        <v>-0.6289</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.3805</v>
+        <v>-0.9822</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.9847</v>
+        <v>-0.7341</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.3958</v>
+        <v>-0.2481</v>
       </c>
       <c r="G6" t="n">
         <v>-1.576</v>
@@ -922,13 +922,13 @@
         <v>0.9264</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.7309</v>
+        <v>-0.3326</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.4377</v>
+        <v>-0.1871</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.2932</v>
+        <v>-0.1455</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. FROUFE PEREZ</t>
+          <t>J. CARO SERRANO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.0292</v>
+        <v>-2.05</v>
       </c>
       <c r="E7" t="n">
-        <v>0.4474</v>
+        <v>-0.3012</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.4766</v>
+        <v>-1.7488</v>
       </c>
       <c r="G7" t="n">
-        <v>1.9964</v>
+        <v>-2.3968</v>
       </c>
       <c r="H7" t="n">
-        <v>3.6664</v>
+        <v>-0.2756</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.6699</v>
+        <v>-2.1212</v>
       </c>
       <c r="J7" t="n">
-        <v>5.4324</v>
+        <v>-0.4626</v>
       </c>
       <c r="K7" t="n">
-        <v>4.2379</v>
+        <v>0.1074</v>
       </c>
       <c r="L7" t="n">
-        <v>1.1945</v>
+        <v>-0.5699</v>
       </c>
       <c r="M7" t="n">
-        <v>-3.4359</v>
+        <v>-1.9343</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.5715</v>
+        <v>-0.383</v>
       </c>
       <c r="O7" t="n">
-        <v>-2.8644</v>
+        <v>-1.5513</v>
       </c>
       <c r="P7" t="n">
-        <v>-1.4823</v>
+        <v>0.5558999999999999</v>
       </c>
       <c r="Q7" t="n">
-        <v>-3.7057</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2.2234</v>
+        <v>0.5558999999999999</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.599</v>
+        <v>0.1054</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.9637</v>
+        <v>0.1614</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.6352</v>
+        <v>-0.056</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.9444</v>
+        <v>-0.3144</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.3155</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.6289</v>
+        <v>-0.3144</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. CARO SERRANO</t>
+          <t>F. VALDIVIA SANTILLANA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.6628</v>
+        <v>-2.6703</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.7909</v>
+        <v>-0.4778</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.8719</v>
+        <v>-2.1925</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.3968</v>
+        <v>-1.8598</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.2756</v>
+        <v>-0.4991</v>
       </c>
       <c r="I8" t="n">
-        <v>-2.1212</v>
+        <v>-1.3608</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.4626</v>
+        <v>-0.0506</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1074</v>
+        <v>-0.1335</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.5699</v>
+        <v>0.0829</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.9343</v>
+        <v>-1.8093</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.383</v>
+        <v>-0.3656</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.5513</v>
+        <v>-1.4437</v>
       </c>
       <c r="P8" t="n">
-        <v>0.5558999999999999</v>
+        <v>2.0382</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.5558999999999999</v>
+        <v>2.0382</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.5074</v>
+        <v>-0.6454</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.3283</v>
+        <v>0.2027</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1791</v>
+        <v>-0.8481</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.3144</v>
+        <v>-2.2033</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>-0.63</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.3144</v>
+        <v>-1.5733</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>F. VALDIVIA SANTILLANA</t>
+          <t>F. NDIAYE</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.6863</v>
+        <v>-4.6533</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.3707</v>
+        <v>-3.2271</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.3156</v>
+        <v>-1.4262</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.8598</v>
+        <v>-7.0354</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.4991</v>
+        <v>-1.9221</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.3608</v>
+        <v>-5.1133</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.0506</v>
+        <v>-4.09</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.1335</v>
+        <v>-2.2558</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0829</v>
+        <v>-1.8342</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.8093</v>
+        <v>-2.9454</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.3656</v>
+        <v>0.3337</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.4437</v>
+        <v>-3.2791</v>
       </c>
       <c r="P9" t="n">
-        <v>2.0382</v>
+        <v>-0.9264</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-3.7057</v>
       </c>
       <c r="R9" t="n">
-        <v>2.0382</v>
+        <v>2.7793</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.6614</v>
+        <v>2.3646</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.6901</v>
+        <v>2.3659</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.9712</v>
+        <v>-0.0013</v>
       </c>
       <c r="V9" t="n">
-        <v>-2.2033</v>
+        <v>0.9439</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.63</v>
+        <v>2.2027</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.5733</v>
+        <v>-1.2589</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-5.5308</v>
+        <v>-4.6909</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.7668</v>
+        <v>-3.2224</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.764</v>
+        <v>-1.4685</v>
       </c>
       <c r="G10" t="n">
         <v>-4.4606</v>
@@ -1234,13 +1234,13 @@
         <v>1.4823</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.6996</v>
+        <v>0.1402</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.2773</v>
+        <v>0.2671</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.4223</v>
+        <v>-0.1269</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-12.1435</v>
+        <v>-11.5961</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.919700000000001</v>
+        <v>-1.372300000000001</v>
       </c>
       <c r="F11" t="n">
-        <v>-10.2237</v>
+        <v>-10.2236</v>
       </c>
       <c r="G11" t="n">
         <v>-17.908</v>
@@ -1285,7 +1285,7 @@
         <v>-21.2735</v>
       </c>
       <c r="J11" t="n">
-        <v>0.8074000000000003</v>
+        <v>0.8074000000000008</v>
       </c>
       <c r="K11" t="n">
         <v>4.9176</v>
@@ -1312,16 +1312,16 @@
         <v>13.8965</v>
       </c>
       <c r="S11" t="n">
-        <v>1.411400000000001</v>
+        <v>1.9586</v>
       </c>
       <c r="T11" t="n">
-        <v>3.9858</v>
+        <v>4.533</v>
       </c>
       <c r="U11" t="n">
-        <v>-2.5742</v>
+        <v>-2.5744</v>
       </c>
       <c r="V11" t="n">
-        <v>1.573900000000001</v>
+        <v>1.5739</v>
       </c>
       <c r="W11" t="n">
         <v>4.4044</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>7.2602</v>
+        <v>7.219</v>
       </c>
       <c r="E12" t="n">
-        <v>7.2345</v>
+        <v>7.1366</v>
       </c>
       <c r="F12" t="n">
-        <v>0.0257</v>
+        <v>0.0824</v>
       </c>
       <c r="G12" t="n">
         <v>7.7956</v>
@@ -1390,13 +1390,13 @@
         <v>1.8529</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.5168</v>
+        <v>-0.5580000000000001</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.1044</v>
+        <v>-0.2024</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.4124</v>
+        <v>-0.3557</v>
       </c>
       <c r="V12" t="n">
         <v>-0.945</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>R. SANCHEZ SANCHEZ</t>
+          <t>R. SANAHUJA TRESERRAS</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>2.3086</v>
+        <v>2.4949</v>
       </c>
       <c r="E13" t="n">
-        <v>1.2591</v>
+        <v>1.8352</v>
       </c>
       <c r="F13" t="n">
-        <v>1.0495</v>
+        <v>0.6597</v>
       </c>
       <c r="G13" t="n">
-        <v>1.9373</v>
+        <v>1.8889</v>
       </c>
       <c r="H13" t="n">
-        <v>0.0464</v>
+        <v>-0.8112</v>
       </c>
       <c r="I13" t="n">
-        <v>1.8908</v>
+        <v>2.7002</v>
       </c>
       <c r="J13" t="n">
-        <v>1.3686</v>
+        <v>1.6996</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>-0.4167</v>
       </c>
       <c r="L13" t="n">
-        <v>1.3686</v>
+        <v>2.1163</v>
       </c>
       <c r="M13" t="n">
-        <v>0.5687</v>
+        <v>0.1893</v>
       </c>
       <c r="N13" t="n">
-        <v>0.0464</v>
+        <v>-0.3945</v>
       </c>
       <c r="O13" t="n">
-        <v>0.5223</v>
+        <v>0.5839</v>
       </c>
       <c r="P13" t="n">
-        <v>0.3706</v>
+        <v>1.4823</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>-0.1853</v>
       </c>
       <c r="R13" t="n">
-        <v>0.3706</v>
+        <v>1.6676</v>
       </c>
       <c r="S13" t="n">
-        <v>0.0007</v>
+        <v>-0.2475</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.1094</v>
+        <v>0.3209</v>
       </c>
       <c r="U13" t="n">
-        <v>0.1102</v>
+        <v>-0.5683</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>-0.6289</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>-0.6289</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>R. SANAHUJA TRESERRAS</t>
+          <t>R. SANCHEZ SANCHEZ</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.8987</v>
+        <v>2.2593</v>
       </c>
       <c r="E14" t="n">
-        <v>1.4435</v>
+        <v>1.2591</v>
       </c>
       <c r="F14" t="n">
-        <v>0.4553</v>
+        <v>1.0002</v>
       </c>
       <c r="G14" t="n">
-        <v>1.8889</v>
+        <v>1.9373</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.8112</v>
+        <v>0.0464</v>
       </c>
       <c r="I14" t="n">
-        <v>2.7002</v>
+        <v>1.8908</v>
       </c>
       <c r="J14" t="n">
-        <v>1.6996</v>
+        <v>1.3686</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.4167</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>2.1163</v>
+        <v>1.3686</v>
       </c>
       <c r="M14" t="n">
-        <v>0.1893</v>
+        <v>0.5687</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.3945</v>
+        <v>0.0464</v>
       </c>
       <c r="O14" t="n">
-        <v>0.5839</v>
+        <v>0.5223</v>
       </c>
       <c r="P14" t="n">
-        <v>1.4823</v>
+        <v>0.3706</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.1853</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.6676</v>
+        <v>0.3706</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.8436</v>
+        <v>-0.0485</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.0709</v>
+        <v>-0.1094</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.7728</v>
+        <v>0.0609</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.6289</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.6289</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A. ARCONES DURAND</t>
+          <t>P. VILLAREJO CALATAYUD</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,64 +1579,64 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.3761</v>
+        <v>1.7131</v>
       </c>
       <c r="E15" t="n">
-        <v>0.6188</v>
+        <v>1.7765</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7573</v>
+        <v>-0.0634</v>
       </c>
       <c r="G15" t="n">
-        <v>2.0634</v>
+        <v>0.8486</v>
       </c>
       <c r="H15" t="n">
-        <v>-1.5047</v>
+        <v>-1.3063</v>
       </c>
       <c r="I15" t="n">
-        <v>3.5682</v>
+        <v>2.1549</v>
       </c>
       <c r="J15" t="n">
-        <v>2.9334</v>
+        <v>2.017</v>
       </c>
       <c r="K15" t="n">
-        <v>0.1027</v>
+        <v>-0.0993</v>
       </c>
       <c r="L15" t="n">
-        <v>2.8307</v>
+        <v>2.1163</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.87</v>
+        <v>-1.1684</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.6074</v>
+        <v>-1.207</v>
       </c>
       <c r="O15" t="n">
-        <v>0.7374000000000001</v>
+        <v>0.0386</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.7411</v>
+        <v>-0.5558999999999999</v>
       </c>
       <c r="Q15" t="n">
         <v>-2.0382</v>
       </c>
       <c r="R15" t="n">
-        <v>1.297</v>
+        <v>1.4823</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.2611</v>
+        <v>-0.4685</v>
       </c>
       <c r="T15" t="n">
-        <v>0.0386</v>
+        <v>0.5387999999999999</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.2997</v>
+        <v>-1.0073</v>
       </c>
       <c r="V15" t="n">
-        <v>0.315</v>
+        <v>1.8888</v>
       </c>
       <c r="W15" t="n">
-        <v>-0.315</v>
+        <v>1.2589</v>
       </c>
       <c r="X15" t="n">
         <v>0.63</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>C. ARANDA SUAREZ</t>
+          <t>A. ARCONES DURAND</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.3153</v>
+        <v>1.3761</v>
       </c>
       <c r="E16" t="n">
-        <v>0.4398</v>
+        <v>0.6188</v>
       </c>
       <c r="F16" t="n">
-        <v>0.8754999999999999</v>
+        <v>0.7573</v>
       </c>
       <c r="G16" t="n">
-        <v>2.9056</v>
+        <v>2.0634</v>
       </c>
       <c r="H16" t="n">
-        <v>1.1252</v>
+        <v>-1.5047</v>
       </c>
       <c r="I16" t="n">
-        <v>1.7804</v>
+        <v>3.5682</v>
       </c>
       <c r="J16" t="n">
-        <v>2.4321</v>
+        <v>2.9334</v>
       </c>
       <c r="K16" t="n">
-        <v>1.5198</v>
+        <v>0.1027</v>
       </c>
       <c r="L16" t="n">
-        <v>0.9124</v>
+        <v>2.8307</v>
       </c>
       <c r="M16" t="n">
-        <v>0.4735</v>
+        <v>-0.87</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.3945</v>
+        <v>-1.6074</v>
       </c>
       <c r="O16" t="n">
-        <v>0.868</v>
+        <v>0.7374000000000001</v>
       </c>
       <c r="P16" t="n">
-        <v>-2.4087</v>
+        <v>-0.7411</v>
       </c>
       <c r="Q16" t="n">
-        <v>-3.891</v>
+        <v>-2.0382</v>
       </c>
       <c r="R16" t="n">
-        <v>1.4823</v>
+        <v>1.297</v>
       </c>
       <c r="S16" t="n">
-        <v>1.7628</v>
+        <v>-0.2611</v>
       </c>
       <c r="T16" t="n">
-        <v>1.5843</v>
+        <v>0.0386</v>
       </c>
       <c r="U16" t="n">
-        <v>0.1785</v>
+        <v>-0.2997</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.9444</v>
+        <v>0.315</v>
       </c>
       <c r="W16" t="n">
-        <v>0.3144</v>
+        <v>-0.315</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.2589</v>
+        <v>0.63</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>R. URBANO MORENO</t>
+          <t>C. ARANDA SUAREZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,58 +1735,58 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.5438</v>
+        <v>0.4397</v>
       </c>
       <c r="E17" t="n">
-        <v>1.0406</v>
+        <v>-0.1477</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.4968</v>
+        <v>0.5875</v>
       </c>
       <c r="G17" t="n">
-        <v>2.2746</v>
+        <v>2.9056</v>
       </c>
       <c r="H17" t="n">
-        <v>1.1212</v>
+        <v>1.1252</v>
       </c>
       <c r="I17" t="n">
-        <v>1.1534</v>
+        <v>1.7804</v>
       </c>
       <c r="J17" t="n">
-        <v>2.3464</v>
+        <v>2.4321</v>
       </c>
       <c r="K17" t="n">
-        <v>1.5157</v>
+        <v>1.5198</v>
       </c>
       <c r="L17" t="n">
-        <v>0.8307</v>
+        <v>0.9124</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.0718</v>
+        <v>0.4735</v>
       </c>
       <c r="N17" t="n">
         <v>-0.3945</v>
       </c>
       <c r="O17" t="n">
-        <v>0.3227</v>
+        <v>0.868</v>
       </c>
       <c r="P17" t="n">
-        <v>-1.4823</v>
+        <v>-2.4087</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.9646</v>
+        <v>-3.891</v>
       </c>
       <c r="R17" t="n">
         <v>1.4823</v>
       </c>
       <c r="S17" t="n">
-        <v>0.6959</v>
+        <v>0.8873</v>
       </c>
       <c r="T17" t="n">
-        <v>1.3443</v>
+        <v>0.9967</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.6484</v>
+        <v>-0.1095</v>
       </c>
       <c r="V17" t="n">
         <v>-0.9444</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>P. VILLAREJO CALATAYUD</t>
+          <t>R. URBANO MORENO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.2098</v>
+        <v>0.3817</v>
       </c>
       <c r="E18" t="n">
-        <v>0.6992</v>
+        <v>0.5508999999999999</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4894</v>
+        <v>-0.1692</v>
       </c>
       <c r="G18" t="n">
-        <v>0.8486</v>
+        <v>2.2746</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.3063</v>
+        <v>1.1212</v>
       </c>
       <c r="I18" t="n">
-        <v>2.1549</v>
+        <v>1.1534</v>
       </c>
       <c r="J18" t="n">
-        <v>2.017</v>
+        <v>2.3464</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.0993</v>
+        <v>1.5157</v>
       </c>
       <c r="L18" t="n">
-        <v>2.1163</v>
+        <v>0.8307</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.1684</v>
+        <v>-0.0718</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.207</v>
+        <v>-0.3945</v>
       </c>
       <c r="O18" t="n">
-        <v>0.0386</v>
+        <v>0.3227</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.5558999999999999</v>
+        <v>-1.4823</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.0382</v>
+        <v>-2.9646</v>
       </c>
       <c r="R18" t="n">
         <v>1.4823</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.9718</v>
+        <v>0.5338000000000001</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.5384</v>
+        <v>0.8546</v>
       </c>
       <c r="U18" t="n">
-        <v>-1.4333</v>
+        <v>-0.3209</v>
       </c>
       <c r="V18" t="n">
-        <v>1.8888</v>
+        <v>-0.9444</v>
       </c>
       <c r="W18" t="n">
-        <v>1.2589</v>
+        <v>0.3144</v>
       </c>
       <c r="X18" t="n">
-        <v>0.63</v>
+        <v>-1.2589</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.5594</v>
+        <v>-0.4609</v>
       </c>
       <c r="E19" t="n">
         <v>-1.5643</v>
       </c>
       <c r="F19" t="n">
-        <v>1.005</v>
+        <v>1.1034</v>
       </c>
       <c r="G19" t="n">
         <v>0.1708</v>
@@ -1936,13 +1936,13 @@
         <v>0.3706</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.1743</v>
+        <v>-0.0759</v>
       </c>
       <c r="T19" t="n">
         <v>-0.1094</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.0649</v>
+        <v>0.0336</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. SHANNON</t>
+          <t>A. ELIAS GALLEGOS</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.8729</v>
+        <v>-1.2391</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.24</v>
+        <v>-0.6096</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.6329</v>
+        <v>-0.6294</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.8253</v>
+        <v>-1.1517</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.0881</v>
+        <v>-0.08409999999999999</v>
       </c>
       <c r="I20" t="n">
-        <v>0.2628</v>
+        <v>-1.0676</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.2225</v>
+        <v>-0.6529</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.5542</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>0.3318</v>
+        <v>-0.6529</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.6028</v>
+        <v>-0.4989</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.5338000000000001</v>
+        <v>-0.08409999999999999</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.06900000000000001</v>
+        <v>-0.4147</v>
       </c>
       <c r="P20" t="n">
-        <v>0.1853</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.9264</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.1117</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>0.08210000000000001</v>
+        <v>-0.08740000000000001</v>
       </c>
       <c r="T20" t="n">
-        <v>0.5944</v>
+        <v>0.0432</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.5124</v>
+        <v>-0.1306</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.315</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>0.3144</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.6294</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. ELIAS GALLEGOS</t>
+          <t>J. SHANNON</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.337</v>
+        <v>-1.3877</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.7076</v>
+        <v>-0.6317</v>
       </c>
       <c r="F21" t="n">
+        <v>-0.756</v>
+      </c>
+      <c r="G21" t="n">
+        <v>-0.8253</v>
+      </c>
+      <c r="H21" t="n">
+        <v>-1.0881</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.2628</v>
+      </c>
+      <c r="J21" t="n">
+        <v>-0.2225</v>
+      </c>
+      <c r="K21" t="n">
+        <v>-0.5542</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0.3318</v>
+      </c>
+      <c r="M21" t="n">
+        <v>-0.6028</v>
+      </c>
+      <c r="N21" t="n">
+        <v>-0.5338000000000001</v>
+      </c>
+      <c r="O21" t="n">
+        <v>-0.06900000000000001</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0.1853</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>-0.9264</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.1117</v>
+      </c>
+      <c r="S21" t="n">
+        <v>-0.4328</v>
+      </c>
+      <c r="T21" t="n">
+        <v>0.2027</v>
+      </c>
+      <c r="U21" t="n">
+        <v>-0.6355</v>
+      </c>
+      <c r="V21" t="n">
+        <v>-0.315</v>
+      </c>
+      <c r="W21" t="n">
+        <v>0.3144</v>
+      </c>
+      <c r="X21" t="n">
         <v>-0.6294</v>
-      </c>
-      <c r="G21" t="n">
-        <v>-1.1517</v>
-      </c>
-      <c r="H21" t="n">
-        <v>-0.08409999999999999</v>
-      </c>
-      <c r="I21" t="n">
-        <v>-1.0676</v>
-      </c>
-      <c r="J21" t="n">
-        <v>-0.6529</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>-0.6529</v>
-      </c>
-      <c r="M21" t="n">
-        <v>-0.4989</v>
-      </c>
-      <c r="N21" t="n">
-        <v>-0.08409999999999999</v>
-      </c>
-      <c r="O21" t="n">
-        <v>-0.4147</v>
-      </c>
-      <c r="P21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>0</v>
-      </c>
-      <c r="R21" t="n">
-        <v>0</v>
-      </c>
-      <c r="S21" t="n">
-        <v>-0.1853</v>
-      </c>
-      <c r="T21" t="n">
-        <v>-0.0547</v>
-      </c>
-      <c r="U21" t="n">
-        <v>-0.1306</v>
-      </c>
-      <c r="V21" t="n">
-        <v>0</v>
-      </c>
-      <c r="W21" t="n">
-        <v>0</v>
-      </c>
-      <c r="X21" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -2125,19 +2125,19 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>12.1432</v>
+        <v>12.7961</v>
       </c>
       <c r="E22" t="n">
-        <v>10.2236</v>
+        <v>10.2238</v>
       </c>
       <c r="F22" t="n">
-        <v>1.9198</v>
+        <v>2.5725</v>
       </c>
       <c r="G22" t="n">
         <v>17.9078</v>
       </c>
       <c r="H22" t="n">
-        <v>-3.3657</v>
+        <v>-3.365699999999999</v>
       </c>
       <c r="I22" t="n">
         <v>21.2736</v>
@@ -2170,13 +2170,13 @@
         <v>11.1173</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.4114</v>
+        <v>-0.7586000000000002</v>
       </c>
       <c r="T22" t="n">
-        <v>2.5744</v>
+        <v>2.5743</v>
       </c>
       <c r="U22" t="n">
-        <v>-3.9858</v>
+        <v>-3.333</v>
       </c>
       <c r="V22" t="n">
         <v>-1.5739</v>
